--- a/database/seeders/xlsx/2402.xlsx
+++ b/database/seeders/xlsx/2402.xlsx
@@ -865,7 +865,7 @@
     <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
-  <fonts count="24">
+  <fonts count="23">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -892,12 +892,6 @@
       <color rgb="FF000000"/>
       <name val="Segoe UI"/>
       <charset val="204"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF555555"/>
-      <name val="Verdana"/>
-      <charset val="134"/>
     </font>
     <font>
       <u/>
@@ -1465,137 +1459,137 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="15" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="15" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1624,15 +1618,6 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1959,10 +1944,11 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:Q42"/>
+  <dimension ref="A1:Q30"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="2" width="5.77777777777778" customWidth="1"/>
+    <col min="1" max="1" width="14.5555555555556" customWidth="1"/>
+    <col min="2" max="2" width="5.77777777777778" customWidth="1"/>
     <col min="3" max="3" width="14.7777777777778" customWidth="1"/>
     <col min="4" max="4" width="9.90740740740741" style="1" customWidth="1"/>
     <col min="5" max="5" width="8.77777777777778" style="1" customWidth="1"/>
@@ -2017,13 +2003,13 @@
       <c r="N1" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="21" t="s">
+      <c r="O1" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="21" t="s">
+      <c r="P1" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="25" t="s">
+      <c r="Q1" s="20" t="s">
         <v>16</v>
       </c>
     </row>
@@ -2351,10 +2337,10 @@
       <c r="H9" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="I9" s="22"/>
-      <c r="J9" s="22"/>
-      <c r="K9" s="22"/>
-      <c r="L9" s="22"/>
+      <c r="I9" s="17"/>
+      <c r="J9" s="17"/>
+      <c r="K9" s="17"/>
+      <c r="L9" s="17"/>
       <c r="M9" s="13">
         <v>1050</v>
       </c>
@@ -2437,10 +2423,10 @@
       <c r="H11" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="I11" s="22"/>
-      <c r="J11" s="22"/>
-      <c r="K11" s="22"/>
-      <c r="L11" s="22"/>
+      <c r="I11" s="17"/>
+      <c r="J11" s="17"/>
+      <c r="K11" s="17"/>
+      <c r="L11" s="17"/>
       <c r="M11" s="13">
         <v>1100</v>
       </c>
@@ -2480,10 +2466,10 @@
       <c r="H12" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="I12" s="22"/>
-      <c r="J12" s="22"/>
-      <c r="K12" s="22"/>
-      <c r="L12" s="22"/>
+      <c r="I12" s="17"/>
+      <c r="J12" s="17"/>
+      <c r="K12" s="17"/>
+      <c r="L12" s="17"/>
       <c r="M12" s="13">
         <v>1150</v>
       </c>
@@ -2523,10 +2509,10 @@
       <c r="H13" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="I13" s="22"/>
-      <c r="J13" s="22"/>
-      <c r="K13" s="22"/>
-      <c r="L13" s="22"/>
+      <c r="I13" s="17"/>
+      <c r="J13" s="17"/>
+      <c r="K13" s="17"/>
+      <c r="L13" s="17"/>
       <c r="M13" s="13">
         <v>800</v>
       </c>
@@ -2566,10 +2552,10 @@
       <c r="H14" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="I14" s="22"/>
-      <c r="J14" s="22"/>
-      <c r="K14" s="22"/>
-      <c r="L14" s="22"/>
+      <c r="I14" s="17"/>
+      <c r="J14" s="17"/>
+      <c r="K14" s="17"/>
+      <c r="L14" s="17"/>
       <c r="M14" s="13">
         <v>1100</v>
       </c>
@@ -2609,10 +2595,10 @@
       <c r="H15" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="I15" s="22"/>
-      <c r="J15" s="22"/>
-      <c r="K15" s="22"/>
-      <c r="L15" s="22"/>
+      <c r="I15" s="17"/>
+      <c r="J15" s="17"/>
+      <c r="K15" s="17"/>
+      <c r="L15" s="17"/>
       <c r="M15" s="13">
         <v>800</v>
       </c>
@@ -2828,13 +2814,13 @@
       <c r="J20" s="5"/>
       <c r="K20" s="5"/>
       <c r="L20" s="5"/>
-      <c r="M20" s="23">
+      <c r="M20" s="18">
         <v>1100</v>
       </c>
       <c r="N20" s="13">
         <v>0</v>
       </c>
-      <c r="O20" s="23">
+      <c r="O20" s="18">
         <v>1100</v>
       </c>
       <c r="P20" s="5">
@@ -2867,17 +2853,17 @@
       <c r="H21" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="I21" s="24"/>
-      <c r="J21" s="24"/>
-      <c r="K21" s="24"/>
-      <c r="L21" s="24"/>
-      <c r="M21" s="23">
+      <c r="I21" s="19"/>
+      <c r="J21" s="19"/>
+      <c r="K21" s="19"/>
+      <c r="L21" s="19"/>
+      <c r="M21" s="18">
         <v>1100</v>
       </c>
       <c r="N21" s="13">
         <v>0</v>
       </c>
-      <c r="O21" s="23">
+      <c r="O21" s="18">
         <v>1100</v>
       </c>
       <c r="P21" s="5">
@@ -2910,17 +2896,17 @@
       <c r="H22" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="I22" s="24"/>
-      <c r="J22" s="24"/>
-      <c r="K22" s="24"/>
-      <c r="L22" s="24"/>
-      <c r="M22" s="23">
+      <c r="I22" s="19"/>
+      <c r="J22" s="19"/>
+      <c r="K22" s="19"/>
+      <c r="L22" s="19"/>
+      <c r="M22" s="18">
         <v>1700</v>
       </c>
       <c r="N22" s="13">
         <v>0</v>
       </c>
-      <c r="O22" s="23">
+      <c r="O22" s="18">
         <v>1700</v>
       </c>
       <c r="P22" s="5">
@@ -2953,17 +2939,17 @@
       <c r="H23" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="I23" s="24"/>
-      <c r="J23" s="24"/>
-      <c r="K23" s="24"/>
-      <c r="L23" s="24"/>
-      <c r="M23" s="23">
+      <c r="I23" s="19"/>
+      <c r="J23" s="19"/>
+      <c r="K23" s="19"/>
+      <c r="L23" s="19"/>
+      <c r="M23" s="18">
         <v>1200</v>
       </c>
       <c r="N23" s="13">
         <v>0</v>
       </c>
-      <c r="O23" s="23">
+      <c r="O23" s="18">
         <v>1200</v>
       </c>
       <c r="P23" s="5">
@@ -2996,17 +2982,17 @@
       <c r="H24" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="I24" s="24"/>
-      <c r="J24" s="24"/>
-      <c r="K24" s="24"/>
-      <c r="L24" s="24"/>
-      <c r="M24" s="23">
+      <c r="I24" s="19"/>
+      <c r="J24" s="19"/>
+      <c r="K24" s="19"/>
+      <c r="L24" s="19"/>
+      <c r="M24" s="18">
         <v>1100</v>
       </c>
       <c r="N24" s="13">
         <v>0</v>
       </c>
-      <c r="O24" s="23">
+      <c r="O24" s="18">
         <v>1100</v>
       </c>
       <c r="P24" s="5">
@@ -3043,13 +3029,13 @@
       <c r="J25" s="5"/>
       <c r="K25" s="5"/>
       <c r="L25" s="5"/>
-      <c r="M25" s="23">
+      <c r="M25" s="18">
         <v>850</v>
       </c>
       <c r="N25" s="13">
         <v>0</v>
       </c>
-      <c r="O25" s="23">
+      <c r="O25" s="18">
         <v>850</v>
       </c>
       <c r="P25" s="5">
@@ -3086,13 +3072,13 @@
       <c r="J26" s="5"/>
       <c r="K26" s="5"/>
       <c r="L26" s="5"/>
-      <c r="M26" s="23">
+      <c r="M26" s="18">
         <v>1050</v>
       </c>
       <c r="N26" s="13">
         <v>0</v>
       </c>
-      <c r="O26" s="23">
+      <c r="O26" s="18">
         <v>1050</v>
       </c>
       <c r="P26" s="5">
@@ -3129,13 +3115,13 @@
       <c r="J27" s="5"/>
       <c r="K27" s="5"/>
       <c r="L27" s="5"/>
-      <c r="M27" s="23">
+      <c r="M27" s="18">
         <v>1000</v>
       </c>
       <c r="N27" s="13">
         <v>0</v>
       </c>
-      <c r="O27" s="23">
+      <c r="O27" s="18">
         <v>1000</v>
       </c>
       <c r="P27" s="5">
@@ -3172,13 +3158,13 @@
       <c r="J28" s="5"/>
       <c r="K28" s="5"/>
       <c r="L28" s="5"/>
-      <c r="M28" s="23">
+      <c r="M28" s="18">
         <v>1200</v>
       </c>
       <c r="N28" s="13">
         <v>0</v>
       </c>
-      <c r="O28" s="23">
+      <c r="O28" s="18">
         <v>1200</v>
       </c>
       <c r="P28" s="5">
@@ -3215,13 +3201,13 @@
       <c r="J29" s="5"/>
       <c r="K29" s="5"/>
       <c r="L29" s="5"/>
-      <c r="M29" s="23">
+      <c r="M29" s="18">
         <v>1200</v>
       </c>
       <c r="N29" s="13">
         <v>0</v>
       </c>
-      <c r="O29" s="23">
+      <c r="O29" s="18">
         <v>1200</v>
       </c>
       <c r="P29" s="5">
@@ -3258,13 +3244,13 @@
       <c r="J30" s="5"/>
       <c r="K30" s="5"/>
       <c r="L30" s="5"/>
-      <c r="M30" s="23">
+      <c r="M30" s="18">
         <v>1200</v>
       </c>
       <c r="N30" s="13">
         <v>0</v>
       </c>
-      <c r="O30" s="23">
+      <c r="O30" s="18">
         <v>1200</v>
       </c>
       <c r="P30" s="5">
@@ -3273,233 +3259,6 @@
       <c r="Q30" s="5">
         <v>1</v>
       </c>
-    </row>
-    <row r="31" spans="1:17">
-      <c r="A31" s="12"/>
-      <c r="B31" s="5"/>
-      <c r="C31" s="5"/>
-      <c r="D31" s="16"/>
-      <c r="E31" s="16"/>
-      <c r="G31" s="5"/>
-      <c r="H31" s="10"/>
-      <c r="I31" s="5"/>
-      <c r="J31" s="5"/>
-      <c r="K31" s="5"/>
-      <c r="L31" s="5"/>
-      <c r="M31" s="5"/>
-      <c r="N31" s="5"/>
-      <c r="O31" s="5"/>
-      <c r="P31" s="5"/>
-      <c r="Q31" s="5"/>
-    </row>
-    <row r="32" spans="1:17">
-      <c r="A32" s="12"/>
-      <c r="B32" s="5"/>
-      <c r="C32" s="5"/>
-      <c r="D32" s="16"/>
-      <c r="E32" s="16"/>
-      <c r="F32" s="15"/>
-      <c r="G32" s="5"/>
-      <c r="H32" s="5"/>
-      <c r="I32" s="5"/>
-      <c r="J32" s="5"/>
-      <c r="K32" s="5"/>
-      <c r="L32" s="5"/>
-      <c r="M32" s="5"/>
-      <c r="N32" s="5"/>
-      <c r="O32" s="5"/>
-      <c r="P32" s="5"/>
-      <c r="Q32" s="5"/>
-    </row>
-    <row r="33" spans="1:17">
-      <c r="A33" s="12"/>
-      <c r="B33" s="5"/>
-      <c r="C33" s="5"/>
-      <c r="D33" s="16"/>
-      <c r="E33" s="16"/>
-      <c r="F33" s="5"/>
-      <c r="G33" s="5"/>
-      <c r="H33" s="5"/>
-      <c r="I33" s="5"/>
-      <c r="J33" s="5"/>
-      <c r="K33" s="5"/>
-      <c r="L33" s="5"/>
-      <c r="M33" s="5"/>
-      <c r="N33" s="5"/>
-      <c r="O33" s="5"/>
-      <c r="P33" s="5"/>
-      <c r="Q33" s="5"/>
-    </row>
-    <row r="34" spans="1:17">
-      <c r="A34" s="12"/>
-      <c r="B34" s="5"/>
-      <c r="C34" s="5"/>
-      <c r="D34" s="16"/>
-      <c r="E34" s="16"/>
-      <c r="F34" s="5"/>
-      <c r="G34" s="5"/>
-      <c r="H34" s="5"/>
-      <c r="I34" s="5"/>
-      <c r="J34" s="5"/>
-      <c r="K34" s="5"/>
-      <c r="L34" s="5"/>
-      <c r="M34" s="5"/>
-      <c r="N34" s="5"/>
-      <c r="O34" s="5"/>
-      <c r="P34" s="5"/>
-      <c r="Q34" s="5"/>
-    </row>
-    <row r="35" spans="1:17">
-      <c r="A35" s="12"/>
-      <c r="B35" s="5"/>
-      <c r="C35" s="5"/>
-      <c r="D35" s="16"/>
-      <c r="E35" s="16"/>
-      <c r="F35" s="5"/>
-      <c r="G35" s="5"/>
-      <c r="H35" s="5"/>
-      <c r="I35" s="5"/>
-      <c r="J35" s="5"/>
-      <c r="K35" s="5"/>
-      <c r="L35" s="5"/>
-      <c r="M35" s="5"/>
-      <c r="N35" s="5"/>
-      <c r="O35" s="5"/>
-      <c r="P35" s="5"/>
-      <c r="Q35" s="5"/>
-    </row>
-    <row r="36" spans="1:17">
-      <c r="A36" s="12"/>
-      <c r="B36" s="5"/>
-      <c r="C36" s="5"/>
-      <c r="D36" s="16"/>
-      <c r="E36" s="16"/>
-      <c r="F36" s="5"/>
-      <c r="G36" s="5"/>
-      <c r="H36" s="5"/>
-      <c r="I36" s="5"/>
-      <c r="J36" s="5"/>
-      <c r="K36" s="5"/>
-      <c r="L36" s="5"/>
-      <c r="M36" s="5"/>
-      <c r="N36" s="5"/>
-      <c r="O36" s="5"/>
-      <c r="P36" s="5"/>
-      <c r="Q36" s="5"/>
-    </row>
-    <row r="37" spans="1:17">
-      <c r="A37" s="12"/>
-      <c r="B37" s="5"/>
-      <c r="C37" s="5"/>
-      <c r="D37" s="16"/>
-      <c r="E37" s="16"/>
-      <c r="F37" s="5"/>
-      <c r="G37" s="5"/>
-      <c r="H37" s="5"/>
-      <c r="I37" s="5"/>
-      <c r="J37" s="5"/>
-      <c r="K37" s="5"/>
-      <c r="L37" s="5"/>
-      <c r="M37" s="5"/>
-      <c r="N37" s="5"/>
-      <c r="O37" s="5"/>
-      <c r="P37" s="5"/>
-      <c r="Q37" s="5"/>
-    </row>
-    <row r="38" spans="1:17">
-      <c r="A38" s="12"/>
-      <c r="B38" s="5"/>
-      <c r="C38" s="5"/>
-      <c r="D38" s="16"/>
-      <c r="E38" s="16"/>
-      <c r="F38" s="5"/>
-      <c r="G38" s="5"/>
-      <c r="H38" s="5"/>
-      <c r="I38" s="5"/>
-      <c r="J38" s="5"/>
-      <c r="K38" s="5"/>
-      <c r="L38" s="5"/>
-      <c r="M38" s="5"/>
-      <c r="N38" s="5"/>
-      <c r="O38" s="5"/>
-      <c r="P38" s="5"/>
-      <c r="Q38" s="5"/>
-    </row>
-    <row r="39" spans="1:17">
-      <c r="A39" s="12"/>
-      <c r="B39" s="5"/>
-      <c r="C39" s="5"/>
-      <c r="D39" s="16"/>
-      <c r="E39" s="16"/>
-      <c r="F39" s="17"/>
-      <c r="G39" s="5"/>
-      <c r="H39" s="5"/>
-      <c r="I39" s="5"/>
-      <c r="J39" s="5"/>
-      <c r="K39" s="5"/>
-      <c r="L39" s="5"/>
-      <c r="M39" s="5"/>
-      <c r="N39" s="5"/>
-      <c r="O39" s="5"/>
-      <c r="P39" s="5"/>
-      <c r="Q39" s="5"/>
-    </row>
-    <row r="40" spans="1:17">
-      <c r="A40" s="12"/>
-      <c r="B40" s="5"/>
-      <c r="C40" s="5"/>
-      <c r="D40" s="16"/>
-      <c r="E40" s="16"/>
-      <c r="F40" s="5"/>
-      <c r="G40" s="5"/>
-      <c r="H40" s="5"/>
-      <c r="I40" s="5"/>
-      <c r="J40" s="5"/>
-      <c r="K40" s="5"/>
-      <c r="L40" s="5"/>
-      <c r="M40" s="5"/>
-      <c r="N40" s="5"/>
-      <c r="O40" s="5"/>
-      <c r="P40" s="5"/>
-      <c r="Q40" s="5"/>
-    </row>
-    <row r="41" spans="1:17">
-      <c r="A41" s="12"/>
-      <c r="B41" s="5"/>
-      <c r="C41" s="5"/>
-      <c r="D41" s="16"/>
-      <c r="E41" s="16"/>
-      <c r="F41" s="5"/>
-      <c r="G41" s="5"/>
-      <c r="H41" s="5"/>
-      <c r="I41" s="5"/>
-      <c r="J41" s="5"/>
-      <c r="K41" s="5"/>
-      <c r="L41" s="5"/>
-      <c r="M41" s="5"/>
-      <c r="N41" s="5"/>
-      <c r="O41" s="5"/>
-      <c r="P41" s="5"/>
-      <c r="Q41" s="5"/>
-    </row>
-    <row r="42" spans="1:17">
-      <c r="A42" s="18"/>
-      <c r="B42" s="19"/>
-      <c r="C42" s="19"/>
-      <c r="D42" s="20"/>
-      <c r="E42" s="20"/>
-      <c r="F42" s="19"/>
-      <c r="G42" s="19"/>
-      <c r="H42" s="19"/>
-      <c r="I42" s="19"/>
-      <c r="J42" s="19"/>
-      <c r="K42" s="19"/>
-      <c r="L42" s="19"/>
-      <c r="M42" s="19"/>
-      <c r="N42" s="19"/>
-      <c r="O42" s="19"/>
-      <c r="P42" s="19"/>
-      <c r="Q42" s="19"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
